--- a/NY_State_Reports_2026-10-16/Fanatics_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-16/Fanatics_Weekly_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA863A9-8CF0-46B9-B7A1-03D385927565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23711AD-3E04-4D66-BF33-69D7BEF19A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
   <sheets>
     <sheet name="FY 26-27" sheetId="7" r:id="rId1"/>
@@ -2949,7 +2949,12 @@
         <v>46306</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="F41" s="33"/>
+      <c r="C41" s="21">
+        <v>68436261.429999992</v>
+      </c>
+      <c r="F41" s="33">
+        <v>6679210.1300000055</v>
+      </c>
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
@@ -3490,11 +3495,11 @@
       </c>
       <c r="C67" s="23">
         <f>SUM(C13:C66)</f>
-        <v>1607413662.3300004</v>
+        <v>1675849923.7600005</v>
       </c>
       <c r="F67" s="23">
         <f>SUM(F13:F66)</f>
-        <v>112286604.88999999</v>
+        <v>118965815.02</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
